--- a/readstore_basic/frontend/streamlit/static/readstore_upload_template.xlsx
+++ b/readstore_basic/frontend/streamlit/static/readstore_upload_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\jona\projects\evobyte\readstore-basic\readstore_basic\frontend\streamlit\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C978D8B-F1DC-416A-832F-D161C9497890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A89EC4C-AF7A-45AE-868E-474C9DF9CFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11664" yWindow="1020" windowWidth="46080" windowHeight="11976" xr2:uid="{55B36872-9D83-4BB5-A16B-39A004B3BA4F}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="46080" windowHeight="12012" xr2:uid="{55B36872-9D83-4BB5-A16B-39A004B3BA4F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>ReadType</t>
   </si>
   <si>
-    <t>UploadPath</t>
-  </si>
-  <si>
-    <t>FASTQFileName</t>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>FilePath</t>
+  </si>
+  <si>
+    <t>ExampleDataset</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>/home/user/example_R1_001.fastq.gz</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>/home/user/example_R2_001.fastq.gz</t>
   </si>
 </sst>
 </file>
@@ -416,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB030E9-C379-4B92-9D5F-A677B7C64ABF}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -427,13 +442,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
